--- a/outputs/evaluation/decision/v1/CF_M01/run_2/CF_M01_decision_eval_gt_report.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M01/run_2/CF_M01_decision_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,49 +471,242 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>CF_M01_AD01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>The goal of this is to improve the security, scalability, and availability of the system.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>*CF_M01_C07, CF_M01_C04, CF_M01_C02</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CF_M01_P03</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Security; Scalability; Availability and reliability</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Service-oriented</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>En el cas de la plataforma de Waapiti, l’arquitectura física no es correspon exactament a l’arquitectura lògica, ja que tant la capa de negoci com la capa de dades es divideixen en diversos serveis diferents. L’objectiu d’això és millorar la seguretat, l’escalabilitat i la disponibilitat del sistema.</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.7478</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>CF_M01_AD03</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Gives the ability to handle partial system crashes</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>*CF_M01_C08</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>CF_M01_AU10</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E3" t="n">
         <v>43</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Resilience</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>API Gateway Service</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>En el cas de la plataforma de Waapiti, l’arquitectura física no es correspon exactament a l’arquitectura lògica, ja que tant la capa de negoci com la capa de dades es divideixen en diversos serveis diferents. L’objectiu d’això és millorar la seguretat, l’escalabilitat i la disponibilitat del sistema.</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.6258</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CF_M01_AD05</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>It was decided to use this language, and not JavaScript, since it is the default language for NestJS and because thanks to its static typing it allows for compile-time error detection.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>*CF_M01_C11</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CF_M01_AU34</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>46</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Maintainability</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>AD_01</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>The physical architecture does not correspond exactly to the logical architecture, as both the business layer and the data layer are divided into several different services. The goal of this is to improve the security, scalability, and availability of the system.</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0.6364</v>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Com a framework es farà ús de NestJS [2], amb el llenguatge Typescript [3], i per la infraestructura es farà ús dels serveis cloud d’AWS [4]. Aquestes tecnologies són les mateixes de les quals s’utilitzen actualment a l’empresa de Waapiti.</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6511</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CF_M01_AD06</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>In this project, this framework has been used to develop the different services that interact with each other. This framework allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>*CF_M01_C11</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CF_M01_AU33</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>46</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Maintainability</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NestJS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>AD_06</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Això és degut de què es segueix el patró de disseny de microserveis Api Gateway [27]. Aquest patró de disseny permet que solament un component sigui qui interactuï entre els usuaris i els serveis que proporciona la plataforma. L’ús d’aquest patró proveeix diversos avantatges al sistema, com poden ser:
+● Augmenta la seguretat del sistema al reduir les portes d’enllaç amb l’exterior, ja que l’única manera d’interactuar amb els microserveis és a través de l’Api Gateway.
+● Dona la capacitat de manegar caigudes parcials del sistema, manegant quins serveis estan en funcionament en tot moment.
+● Éssolament l’Api Gateway que s’encarreguen de l’autorització i el SSL amb el client.</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.7333</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CF_M01_AD07</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CF_M01_C01</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CF_M01_AU16</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Speed and latency</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>AWS cloud services set</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>AD_09</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>S’ha decidit la utilització d’AWS i no altres serveis cloud pel seu baix preu i la seva utilització prèvia per part de l’empresa.</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.6481</v>
       </c>
     </row>
   </sheetData>
